--- a/out_blind/normalized_review.xlsx
+++ b/out_blind/normalized_review.xlsx
@@ -622,7 +622,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r3</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r3</t>
         </is>
       </c>
     </row>
@@ -685,7 +685,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r4</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r4</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r5</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r5</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r6</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r6</t>
         </is>
       </c>
     </row>
@@ -885,7 +885,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r7</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r7</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r8</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r8</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r9</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r9</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r10</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r10</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r11</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r11</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r12</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r12</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r13</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r13</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r14</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r14</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r15</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r15</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r16</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r16</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r17</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r17</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r18</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r18</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r19</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r19</t>
         </is>
       </c>
     </row>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r20</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r20</t>
         </is>
       </c>
     </row>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r21</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r21</t>
         </is>
       </c>
     </row>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r22</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r22</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r23</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r23</t>
         </is>
       </c>
     </row>
@@ -1963,7 +1963,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r24</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r24</t>
         </is>
       </c>
     </row>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r25</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r25</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r26</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r26</t>
         </is>
       </c>
     </row>
@@ -2152,7 +2152,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r27</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r27</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r28</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r28</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r29</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r29</t>
         </is>
       </c>
     </row>
@@ -2341,7 +2341,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r30</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r30</t>
         </is>
       </c>
     </row>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r31</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r31</t>
         </is>
       </c>
     </row>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r32</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r32</t>
         </is>
       </c>
     </row>
@@ -2530,7 +2530,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r33</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r33</t>
         </is>
       </c>
     </row>
@@ -2600,7 +2600,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r34</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r34</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r35</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r35</t>
         </is>
       </c>
     </row>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r36</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r36</t>
         </is>
       </c>
     </row>
@@ -2789,7 +2789,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r37</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r37</t>
         </is>
       </c>
     </row>
@@ -2852,7 +2852,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r38</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r38</t>
         </is>
       </c>
     </row>
@@ -2915,7 +2915,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r39</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r39</t>
         </is>
       </c>
     </row>
@@ -2978,7 +2978,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r40</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r40</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r41</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r41</t>
         </is>
       </c>
     </row>
@@ -3104,7 +3104,7 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r42</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r42</t>
         </is>
       </c>
     </row>
@@ -3167,7 +3167,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r43</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r43</t>
         </is>
       </c>
     </row>
@@ -3230,7 +3230,7 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r44</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r44</t>
         </is>
       </c>
     </row>
@@ -3293,7 +3293,7 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r45</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r45</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r46</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r46</t>
         </is>
       </c>
     </row>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r47</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r47</t>
         </is>
       </c>
     </row>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r48</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r48</t>
         </is>
       </c>
     </row>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r49</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r49</t>
         </is>
       </c>
     </row>
@@ -3608,7 +3608,7 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r50</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r50</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r51</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r51</t>
         </is>
       </c>
     </row>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r52</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r52</t>
         </is>
       </c>
     </row>
@@ -3801,7 +3801,7 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r53</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r53</t>
         </is>
       </c>
     </row>
@@ -3864,7 +3864,7 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r54</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r54</t>
         </is>
       </c>
     </row>
@@ -3927,7 +3927,7 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r55</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r55</t>
         </is>
       </c>
     </row>
@@ -3994,7 +3994,7 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r56</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r56</t>
         </is>
       </c>
     </row>
@@ -4057,7 +4057,7 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r57</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r57</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r58</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r58</t>
         </is>
       </c>
     </row>
@@ -4183,7 +4183,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r59</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r59</t>
         </is>
       </c>
     </row>
@@ -4246,7 +4246,7 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r60</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r60</t>
         </is>
       </c>
     </row>
@@ -4309,7 +4309,7 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r61</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r61</t>
         </is>
       </c>
     </row>
@@ -4372,7 +4372,7 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r62</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r62</t>
         </is>
       </c>
     </row>
@@ -4438,7 +4438,7 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r63</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r63</t>
         </is>
       </c>
     </row>
@@ -4505,7 +4505,7 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r64</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r64</t>
         </is>
       </c>
     </row>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r65</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r65</t>
         </is>
       </c>
     </row>
@@ -4631,7 +4631,7 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r66</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r66</t>
         </is>
       </c>
     </row>
@@ -4694,7 +4694,7 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r67</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r67</t>
         </is>
       </c>
     </row>
@@ -4757,7 +4757,7 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r68</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r68</t>
         </is>
       </c>
     </row>
@@ -4824,7 +4824,7 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r69</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r69</t>
         </is>
       </c>
     </row>
@@ -4887,7 +4887,7 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r70</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r70</t>
         </is>
       </c>
     </row>
@@ -4950,7 +4950,7 @@
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r71</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r71</t>
         </is>
       </c>
     </row>
@@ -5013,7 +5013,7 @@
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r72</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r72</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r73</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r73</t>
         </is>
       </c>
     </row>
@@ -5139,7 +5139,7 @@
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r74</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r74</t>
         </is>
       </c>
     </row>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r75</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r75</t>
         </is>
       </c>
     </row>
@@ -5265,7 +5265,7 @@
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r76</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r76</t>
         </is>
       </c>
     </row>
@@ -5331,7 +5331,7 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r77</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r77</t>
         </is>
       </c>
     </row>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r78</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r78</t>
         </is>
       </c>
     </row>
@@ -5461,7 +5461,7 @@
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r79</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r79</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r80</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r80</t>
         </is>
       </c>
     </row>
@@ -5587,7 +5587,7 @@
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r81</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r81</t>
         </is>
       </c>
     </row>
@@ -5650,7 +5650,7 @@
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r82</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r82</t>
         </is>
       </c>
     </row>
@@ -5713,7 +5713,7 @@
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r83</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r83</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r84</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r84</t>
         </is>
       </c>
     </row>
@@ -5842,7 +5842,7 @@
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r85</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r85</t>
         </is>
       </c>
     </row>
@@ -5909,7 +5909,7 @@
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r86</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r86</t>
         </is>
       </c>
     </row>
@@ -5972,7 +5972,7 @@
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r87</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r87</t>
         </is>
       </c>
     </row>
@@ -6035,7 +6035,7 @@
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r88</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r88</t>
         </is>
       </c>
     </row>
@@ -6098,7 +6098,7 @@
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r89</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r89</t>
         </is>
       </c>
     </row>
@@ -6161,7 +6161,7 @@
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r90</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r90</t>
         </is>
       </c>
     </row>
@@ -6224,7 +6224,7 @@
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r91</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r91</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r92</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r92</t>
         </is>
       </c>
     </row>
@@ -6353,7 +6353,7 @@
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r93</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r93</t>
         </is>
       </c>
     </row>
@@ -6416,7 +6416,7 @@
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r94</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r94</t>
         </is>
       </c>
     </row>
@@ -6479,7 +6479,7 @@
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r95</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r95</t>
         </is>
       </c>
     </row>
@@ -6542,7 +6542,7 @@
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r96</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r96</t>
         </is>
       </c>
     </row>
@@ -6605,7 +6605,7 @@
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r97</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r97</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r98</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r98</t>
         </is>
       </c>
     </row>
@@ -6731,7 +6731,7 @@
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r99</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r99</t>
         </is>
       </c>
     </row>
@@ -6794,7 +6794,7 @@
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r100</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r100</t>
         </is>
       </c>
     </row>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r101</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r101</t>
         </is>
       </c>
     </row>
@@ -6920,7 +6920,7 @@
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r102</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r102</t>
         </is>
       </c>
     </row>
@@ -6983,7 +6983,7 @@
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r103</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r103</t>
         </is>
       </c>
     </row>
@@ -7046,7 +7046,7 @@
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r104</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r104</t>
         </is>
       </c>
     </row>
@@ -7109,7 +7109,7 @@
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r105</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r105</t>
         </is>
       </c>
     </row>
@@ -7172,7 +7172,7 @@
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r106</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r106</t>
         </is>
       </c>
     </row>
@@ -7239,7 +7239,7 @@
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r107</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r107</t>
         </is>
       </c>
     </row>
@@ -7302,7 +7302,7 @@
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r108</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r108</t>
         </is>
       </c>
     </row>
@@ -7365,7 +7365,7 @@
       </c>
       <c r="X108" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r109</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r109</t>
         </is>
       </c>
     </row>
@@ -7432,7 +7432,7 @@
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r110</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r110</t>
         </is>
       </c>
     </row>
@@ -7495,7 +7495,7 @@
       </c>
       <c r="X110" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r111</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r111</t>
         </is>
       </c>
     </row>
@@ -7558,7 +7558,7 @@
       </c>
       <c r="X111" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r112</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r112</t>
         </is>
       </c>
     </row>
@@ -7625,7 +7625,7 @@
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r113</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r113</t>
         </is>
       </c>
     </row>
@@ -7688,7 +7688,7 @@
       </c>
       <c r="X113" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r114</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r114</t>
         </is>
       </c>
     </row>
@@ -7751,7 +7751,7 @@
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>inputs\7249\IO_parsed.xlsx:Append1:r115</t>
+          <t>inputs\tested\7249\IO_parsed.xlsx:Append1:r115</t>
         </is>
       </c>
     </row>
